--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260703.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260703.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>42,424,027</t>
+          <t>42,572,027</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>63.86%</t>
+          <t>63.78%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2,561,703</t>
+          <t>2,570,703</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.80%</t>
+          <t>6.61%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>21,249,000</t>
+          <t>21,323,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.14%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>5,773,267</t>
+          <t>5,794,267</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
@@ -699,56 +699,56 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>20,298,286</t>
+          <t>20,369,286</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.13%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>2,740,608</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>498,000</t>
+          <t>2,749,608</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2,295,901</t>
+          <t>2,303,901</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>4,599,285</t>
+          <t>4,615,285</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>557,222</t>
+          <t>559,222</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>5,383,296</t>
+          <t>5,402,296</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>180,515</t>
+          <t>181,515</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>12,773,134</t>
+          <t>12,818,134</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>5,254,520</t>
+          <t>5,272,520</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -931,110 +931,110 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>1,985,288</t>
+          <t>1,332,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>1,174,617</t>
+          <t>1,992,288</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>1,327,000</t>
+          <t>1,178,617</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>3,403,000</t>
+          <t>600,600</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>598,600</t>
+          <t>3,415,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>139,482</t>
+          <t>140,482</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>163,000</t>
+          <t>164,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>99,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>850,349</t>
+          <t>853,349</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>136,921</t>
+          <t>137,921</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,892,321</t>
+          <t>1,898,321</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>310,672</t>
+          <t>312,672</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>993,822</t>
+          <t>997,822</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>151,499</t>
+          <t>152,499</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>573,000</t>
+          <t>575,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>3,196,000</t>
+          <t>3,207,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1293,56 +1293,56 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>373,000</t>
+          <t>374,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>5,674,000</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>801,897</t>
+          <t>5,694,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1359,34 +1359,34 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,818,000</t>
+          <t>1,824,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>804,897</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,187,441</t>
+          <t>1,191,441</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>763,000</t>
+          <t>766,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1447,51 +1447,51 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>577,000</t>
+          <t>579,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>10,515,121</t>
+          <t>145,386</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>929,659</t>
+          <t>1,372,384</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>144,386</t>
+          <t>10,551,121</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,39 +1525,39 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>3,451,981</t>
+          <t>932,659</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,367,384</t>
+          <t>3,464,981</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>4,418,578</t>
+          <t>4,433,578</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>493,000</t>
+          <t>2,585,703</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>2,576,703</t>
+          <t>495,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>7,111,249</t>
+          <t>7,136,249</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,39 +1657,39 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>202607WVHFN6F</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>2,180,107</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>2,172,107</t>
+          <t>772,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>202607WVHFN6F</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>770,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>180,000</t>
+          <t>181,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>288,000</t>
+          <t>4,936,956</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>798,000</t>
+          <t>1,180,076</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>4,919,956</t>
+          <t>801,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,39 +1811,39 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>1,175,076</t>
+          <t>93,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>1,547,400</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>387,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>1,552,400</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,22 +1899,22 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>387,000</t>
+          <t>289,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>317,000</t>
+          <t>318,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,39 +1943,39 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>155,000</t>
+          <t>998,121</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>995,121</t>
+          <t>170,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>1,743,000</t>
+          <t>65,538</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>169,000</t>
+          <t>177,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>1,749,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>176,000</t>
+          <t>156,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>252,000</t>
+          <t>330,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>329,000</t>
+          <t>253,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>674,000</t>
+          <t>334,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>333,000</t>
+          <t>677,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>71,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>71,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>386,890,738</t>
+          <t>865,356,579</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr"/>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>449,106,287</t>
+          <t>451,039,287</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>-177,841,829</t>
+          <t>-590,273,742</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr"/>
